--- a/docs/pension_data_combined_2026-09-18.xlsx
+++ b/docs/pension_data_combined_2026-09-18.xlsx
@@ -1074,7 +1074,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1.2011</v>
+        <v>1.2002</v>
       </c>
       <c r="D39" t="n">
         <v>2951574</v>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>2.3882</v>
+        <v>2.389</v>
       </c>
       <c r="D40" t="n">
         <v>42446915</v>
@@ -1110,7 +1110,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>2.3669</v>
+        <v>2.3685</v>
       </c>
       <c r="D41" t="n">
         <v>136694375</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>2.3709</v>
+        <v>2.3715</v>
       </c>
       <c r="D42" t="n">
         <v>337218208</v>
@@ -1146,7 +1146,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>2.3995</v>
+        <v>2.4003</v>
       </c>
       <c r="D43" t="n">
         <v>432144529</v>
@@ -1164,7 +1164,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>2.0531</v>
+        <v>2.053</v>
       </c>
       <c r="D44" t="n">
         <v>346990459</v>
@@ -1182,7 +1182,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1.5503</v>
+        <v>1.5481</v>
       </c>
       <c r="D45" t="n">
         <v>256456368</v>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1.2064</v>
+        <v>1.2043</v>
       </c>
       <c r="D46" t="n">
         <v>56754195</v>
@@ -1228,7 +1228,7 @@
         <v>1.1595</v>
       </c>
       <c r="D48" t="n">
-        <v>4138055.48</v>
+        <v>4145170.33</v>
       </c>
     </row>
     <row r="49">
@@ -1246,7 +1246,7 @@
         <v>2.172</v>
       </c>
       <c r="D49" t="n">
-        <v>71858857.54000001</v>
+        <v>71846162.88</v>
       </c>
     </row>
     <row r="50">
@@ -1264,7 +1264,7 @@
         <v>2.1921</v>
       </c>
       <c r="D50" t="n">
-        <v>232711310.25</v>
+        <v>232721644.9</v>
       </c>
     </row>
     <row r="51">
@@ -1282,7 +1282,7 @@
         <v>2.2109</v>
       </c>
       <c r="D51" t="n">
-        <v>355536966.82</v>
+        <v>355540771.1</v>
       </c>
     </row>
     <row r="52">
@@ -1300,7 +1300,7 @@
         <v>2.2157</v>
       </c>
       <c r="D52" t="n">
-        <v>432969349.97</v>
+        <v>432940917.1</v>
       </c>
     </row>
     <row r="53">
@@ -1318,7 +1318,7 @@
         <v>1.9741</v>
       </c>
       <c r="D53" t="n">
-        <v>397364079.89</v>
+        <v>397363100.7</v>
       </c>
     </row>
     <row r="54">
@@ -1336,7 +1336,7 @@
         <v>1.5277</v>
       </c>
       <c r="D54" t="n">
-        <v>316847801.29</v>
+        <v>316582011.7</v>
       </c>
     </row>
     <row r="55">
@@ -1354,7 +1354,7 @@
         <v>1.1866</v>
       </c>
       <c r="D55" t="n">
-        <v>59147440.29</v>
+        <v>59082497.63</v>
       </c>
     </row>
   </sheetData>

--- a/docs/pension_data_combined_2026-09-18.xlsx
+++ b/docs/pension_data_combined_2026-09-18.xlsx
@@ -1224,9 +1224,6 @@
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="C48" t="n">
-        <v>1.1595</v>
-      </c>
       <c r="D48" t="n">
         <v>4145170.33</v>
       </c>
@@ -1349,9 +1346,6 @@
         <is>
           <t>2026-09-18</t>
         </is>
-      </c>
-      <c r="C55" t="n">
-        <v>1.1866</v>
       </c>
       <c r="D55" t="n">
         <v>59082497.63</v>
